--- a/output/pdf_financials_xlsx/ATS.xlsx
+++ b/output/pdf_financials_xlsx/ATS.xlsx
@@ -954,19 +954,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-656</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-1.923</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-5.108</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-2.065</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-1.621</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -975,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-1.979</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-6.049</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>50105</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>46383</v>
+        <v>47039</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>61.696</v>
+        <v>63.619</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>93.886</v>
+        <v>98.994</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>67.539</v>
+        <v>69.604</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>79.45699999999999</v>
+        <v>81.078</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>154.411</v>
@@ -1805,10 +1805,10 @@
         <v>159.771</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>246.687</v>
+        <v>248.666</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-82.938</v>
+        <v>-76.889</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>99.20099999999999</v>
@@ -1884,19 +1884,19 @@
         <v>50134.681</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>46407.07</v>
+        <v>47063.07</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>88.011</v>
+        <v>89.934</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>124.14</v>
+        <v>129.248</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>108.353</v>
+        <v>110.418</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>119.444</v>
+        <v>121.065</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>226.713</v>
@@ -1905,10 +1905,10 @@
         <v>235.61</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>329.75</v>
+        <v>331.729</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.234</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>189.783</v>
@@ -1934,19 +1934,19 @@
         <v>4.822311665576546</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.590650546441601</v>
+        <v>4.655542959568861</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>7.89385880727938</v>
+        <v>8.066336003157149</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.902553892100931</v>
+        <v>10.31001518806397</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.57854258204673</v>
+        <v>7.72297504291008</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>8.35242354823461</v>
+        <v>8.465776069681382</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>10.38673359853797</v>
@@ -1955,10 +1955,10 @@
         <v>9.141439537143087</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.87249326795659</v>
+        <v>10.93774471352835</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.08818578858779579</v>
+        <v>0.3269663772930673</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>6.383697978964873</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>0</v>
+        <v>3.815</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0</v>
+        <v>3.372</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>5.259</v>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>3.815</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>3.372</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>5.259</v>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>62.219</v>
+        <v>58.404</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>55.096</v>
+        <v>51.724</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>148.713</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>5.139</v>
+        <v>1.324</v>
       </c>
       <c r="C77" s="3" t="n">
-        <v>289.526</v>
+        <v>286.154</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>316.12</v>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>5.139</v>
+        <v>1.324</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>289.526</v>
+        <v>286.154</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>316.12</v>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>193.488</v>
+        <v>197.303</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>305.32</v>
+        <v>308.692</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>67.992</v>
@@ -6335,25 +6335,25 @@
         <v>-5.175</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>-17.087</v>
+        <v>-31.62</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>-742.091</v>
+        <v>-757.295</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-158.626</v>
+        <v>-178.173</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-344.169</v>
+        <v>-365.152</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-798.378</v>
+        <v>-824.458</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-573.777</v>
+        <v>-604.296</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-331.424</v>
+        <v>-366.1</v>
       </c>
     </row>
     <row r="125">
@@ -6385,25 +6385,25 @@
         <v>-4.84</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>233.096</v>
+        <v>218.563</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-237.776</v>
+        <v>-252.98</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>587.597</v>
+        <v>568.05</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>51.39</v>
+        <v>30.407</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>18.136</v>
+        <v>-7.944</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>333.238</v>
+        <v>302.719</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-246.425</v>
+        <v>-281.101</v>
       </c>
     </row>
     <row r="126">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">
@@ -27446,7 +27446,11 @@
           <t>Principal lease payments</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -34991,7 +34995,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -35153,7 +35157,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -39778,7 +39782,11 @@
           <t>Interest expense1 $</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -39938,7 +39946,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -40821,7 +40829,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -40904,7 +40912,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -41542,7 +41550,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -41625,7 +41633,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">

--- a/output/pdf_financials_xlsx/ATS.xlsx
+++ b/output/pdf_financials_xlsx/ATS.xlsx
@@ -1001,37 +1001,37 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-26652</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>-25552</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-23.766</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-20.909</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>-28.074</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>-40.152</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-32.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>-62.718</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-68.70399999999999</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-92.194</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-99.57899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1781,37 +1781,37 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>50105</v>
+        <v>76757</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>47039</v>
+        <v>72591</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>63.619</v>
+        <v>87.38500000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>98.994</v>
+        <v>119.903</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>69.604</v>
+        <v>97.678</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>81.078</v>
+        <v>121.23</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>154.411</v>
+        <v>186.611</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>159.771</v>
+        <v>222.489</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>248.666</v>
+        <v>317.37</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-76.889</v>
+        <v>15.305</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>99.20099999999999</v>
+        <v>198.78</v>
       </c>
     </row>
     <row r="28">
@@ -1831,37 +1831,37 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>29.681</v>
+        <v>39.362</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>24.07</v>
+        <v>34.562</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>26.315</v>
+        <v>36.667</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>30.254</v>
+        <v>42.391</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>40.814</v>
+        <v>55.489</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>39.987</v>
+        <v>54.807</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>72.30200000000001</v>
+        <v>93.21899999999999</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>75.839</v>
+        <v>101.429</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>83.063</v>
+        <v>111.518</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>85.172</v>
+        <v>118.846</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>90.58199999999999</v>
+        <v>125.052</v>
       </c>
     </row>
     <row r="29">
@@ -1881,37 +1881,37 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>50134.681</v>
+        <v>76796.36199999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>47063.07</v>
+        <v>72625.56200000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>89.934</v>
+        <v>124.052</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>129.248</v>
+        <v>162.294</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>110.418</v>
+        <v>153.167</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>121.065</v>
+        <v>176.037</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>226.713</v>
+        <v>279.83</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>235.61</v>
+        <v>323.918</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>331.729</v>
+        <v>428.888</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8.282999999999999</v>
+        <v>134.151</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>189.783</v>
+        <v>323.832</v>
       </c>
     </row>
     <row r="30">
@@ -1931,37 +1931,37 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.822311665576546</v>
+        <v>7.386822553960987</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.655542959568861</v>
+        <v>7.184219470889422</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.066336003157149</v>
+        <v>11.12643843111227</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>10.31001518806397</v>
+        <v>12.94606960983267</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.72297504291008</v>
+        <v>10.71297178356254</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>8.465776069681382</v>
+        <v>12.3098320900219</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.38673359853797</v>
+        <v>12.82026025361969</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9.141439537143087</v>
+        <v>12.56770430793394</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.93774471352835</v>
+        <v>14.141264269014</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0.3269663772930673</v>
+        <v>5.29552897262372</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.383697978964873</v>
+        <v>10.89268103004038</v>
       </c>
     </row>
     <row r="31">
@@ -5123,37 +5123,37 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>39.362</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>34.562</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>36.667</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>42.391</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>55.489</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>54.807</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>93.21899999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>101.429</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>111.518</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>118.846</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>125.052</v>
       </c>
     </row>
     <row r="101">
@@ -5723,37 +5723,37 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>22.323</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>5.209</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>11.963</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>23.211</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>5.532</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="113">
@@ -25914,7 +25914,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -26052,7 +26056,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -26760,7 +26764,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -29319,7 +29327,11 @@
           <t>Proceeds from disposal of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -29888,7 +29900,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -29969,7 +29985,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -30787,7 +30803,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -30868,7 +30888,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -31425,7 +31445,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -31506,7 +31530,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -32673,7 +32697,11 @@
           <t>Net finance costs 24</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -33644,7 +33672,11 @@
           <t>Net finance costs 24</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -34197,7 +34229,11 @@
           <t>Depreciation of property, plant and equipment $</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -34276,7 +34312,11 @@
           <t>TO Amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>
@@ -34434,7 +34474,11 @@
           <t>Depreciation of property, plant and equipment $</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -34594,7 +34638,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -38266,7 +38310,11 @@
           <t>Net finance costs 24</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -39470,7 +39518,11 @@
           <t>Net ﬁnance costs 23</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -40187,7 +40239,11 @@
           <t>Net finance costs 23</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -40428,7 +40484,11 @@
           <t>Net finance costs 22</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -41230,7 +41290,11 @@
           <t>Net finance costs 20</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATS.xlsx
+++ b/output/pdf_financials_xlsx/ATS.xlsx
@@ -901,37 +901,37 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>79395</v>
+        <v>76757</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>78749</v>
+        <v>71935</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>93.738</v>
+        <v>85.462</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>124.645</v>
+        <v>114.795</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>128.482</v>
+        <v>95.613</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>148.244</v>
+        <v>119.609</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>225.322</v>
+        <v>186.611</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>280.568</v>
+        <v>222.489</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>351.971</v>
+        <v>315.391</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42.406</v>
+        <v>9.256</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>230.595</v>
+        <v>198.78</v>
       </c>
     </row>
     <row r="12">
@@ -5423,37 +5423,37 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-30.814</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>56.541</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-26.961</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>2.464</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-112.57</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>77.551</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-14.298</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-109.406</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-275.636</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-7.968</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>246.587</v>
       </c>
     </row>
     <row r="107">
@@ -5923,37 +5923,37 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-5.611</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-8.006</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-6.124</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-19.824</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-11.119</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-10.031</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-16.957</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-24.192</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-29.628</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-44.078</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-43.134</v>
       </c>
     </row>
     <row r="117">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-6.032</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -6182,28 +6182,28 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-39.279</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-4.785</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-8.662000000000001</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-21.071</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.014</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-44.983</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="122">
@@ -25835,7 +25835,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -26328,7 +26332,11 @@
           <t>Change in non-cash operating working capital 26</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -26541,7 +26549,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -27310,7 +27322,11 @@
           <t>Repurchase of common shares 17</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -27998,7 +28014,11 @@
           <t>— Net income (loss) $</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -28634,7 +28654,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -28879,7 +28903,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -29738,7 +29766,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -30315,7 +30347,11 @@
           <t>Acquisition of intangible assets 11</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -30394,7 +30430,11 @@
           <t>Repurchase of common shares 16</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -31289,7 +31329,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -31852,7 +31896,11 @@
           <t>Repurchase of common shares 15</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -32634,7 +32682,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -33597,7 +33649,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -38231,7 +38287,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
